--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 07/NKSX_VNSH03_010726.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 07/NKSX_VNSH03_010726.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Nhập kho\Tháng 07\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D05642B-80F1-4D17-8C24-90895D4A3A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE33777D-353A-4F96-A270-17E82E8E6923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
